--- a/src/Precios final.xlsx
+++ b/src/Precios final.xlsx
@@ -1,12 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\mafalda-grafica\src\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Precios final" sheetId="1" r:id="rId5"/>
+    <sheet name="Precios final" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -835,51 +843,27 @@
     <t>IL64</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ILUSTRACIÓN 170G - DOBLE FAZ</t>
-  </si>
-  <si>
     <t>IL65</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ILUSTRACIÓN 210G</t>
-  </si>
-  <si>
     <t>IL66</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ILUSTRACIÓN 210G - DOBLE FAZ</t>
-  </si>
-  <si>
     <t>IL67</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ILUSTRACIÓN 300G</t>
-  </si>
-  <si>
     <t>IL68</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ILUSTRACIÓN 300G - DOBLE FAZ</t>
-  </si>
-  <si>
     <t>IL69</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ADHESIVO OPACO</t>
-  </si>
-  <si>
     <t>IL70</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - ADHESIVO ILUSTRACIÓN</t>
-  </si>
-  <si>
     <t>IL71</t>
   </si>
   <si>
-    <t>LASER - A3 -  BYN - KRAFT 200G</t>
-  </si>
-  <si>
     <t>IL72</t>
   </si>
   <si>
@@ -973,30 +957,18 @@
     <t>VR01</t>
   </si>
   <si>
-    <t>VINILO ROTULADO M2 COLOR + POSICIONADOR</t>
-  </si>
-  <si>
     <t>ROTULADO</t>
   </si>
   <si>
     <t>VR02</t>
   </si>
   <si>
-    <t>VINILO ROTULADO M2 CROMADO ORO + POSICIONADOR</t>
-  </si>
-  <si>
     <t>VR03</t>
   </si>
   <si>
-    <t>VINILO ROTULADO M2 TORNASOLADO + POSICIONADOR</t>
-  </si>
-  <si>
     <t>VR04</t>
   </si>
   <si>
-    <t>VINILO ROTULADO M2 ESMERILADO + POSICIONADOR</t>
-  </si>
-  <si>
     <t>VR05</t>
   </si>
   <si>
@@ -2153,29 +2125,66 @@
   </si>
   <si>
     <t>DUPLICADORA A4 - 5000 HOJAS DOBLE FAZ</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ILUSTRACIÓN 300G - DOBLE FAZ</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ILUSTRACIÓN 170G - DOBLE FAZ</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ILUSTRACIÓN 210G</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ILUSTRACIÓN 210G - DOBLE FAZ</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ILUSTRACIÓN 300G</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ADHESIVO OPACO</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - ADHESIVO ILUSTRACIÓN</t>
+  </si>
+  <si>
+    <t>LASER - A3 - BYN - KRAFT 200G</t>
+  </si>
+  <si>
+    <t>VINILO ROTULADO M LINEAL COLOR + POSICIONADOR</t>
+  </si>
+  <si>
+    <t>VINILO ROTULADO M LINEAL CROMADO ORO + POSICIONADOR</t>
+  </si>
+  <si>
+    <t>VINILO ROTULADO M LINEAL TORNASOLADO + POSICIONADOR</t>
+  </si>
+  <si>
+    <t>VINILO ROTULADO M LINEAL ESMERILADO + POSICIONADOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -2185,44 +2194,49 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2230,7 +2244,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2420,17 +2434,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H347"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2456,7 +2477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2464,17 +2485,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1">
+        <v>700</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2482,17 +2505,19 @@
         <v>12</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1">
+        <v>1400</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -2500,17 +2525,19 @@
         <v>14</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1">
+        <v>500</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2518,17 +2545,19 @@
         <v>16</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1">
+        <v>1000</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -2536,17 +2565,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>1500</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2554,17 +2585,19 @@
         <v>20</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>2000</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -2572,17 +2605,19 @@
         <v>22</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>1600</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -2590,17 +2625,19 @@
         <v>24</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>2200</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -2608,17 +2645,19 @@
         <v>26</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>1700</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -2626,17 +2665,19 @@
         <v>28</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>2400</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -2644,17 +2685,19 @@
         <v>30</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>1500</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -2662,17 +2705,19 @@
         <v>32</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1">
+        <v>2000</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -2680,17 +2725,19 @@
         <v>34</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>2600</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -2698,17 +2745,19 @@
         <v>36</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>2200</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -2716,17 +2765,19 @@
         <v>38</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>1700</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -2734,17 +2785,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <v>1800</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -2752,17 +2805,19 @@
         <v>42</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1">
+        <v>2200</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -2770,17 +2825,19 @@
         <v>44</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1">
+        <v>1800</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -2788,17 +2845,19 @@
         <v>46</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="D20" s="1">
+        <v>2200</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -2806,17 +2865,19 @@
         <v>48</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="1">
+        <v>1500</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -2824,17 +2885,19 @@
         <v>50</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1">
+        <v>2000</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -2842,17 +2905,19 @@
         <v>52</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1">
+        <v>7500</v>
+      </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -2860,17 +2925,19 @@
         <v>54</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="D24" s="1">
+        <v>1900</v>
+      </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -2878,17 +2945,19 @@
         <v>56</v>
       </c>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" s="1">
+        <v>1900</v>
+      </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -2896,17 +2965,19 @@
         <v>58</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="D26" s="1">
+        <v>600</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,17 +2985,19 @@
         <v>60</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="D27" s="1">
+        <v>800</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -2932,17 +3005,19 @@
         <v>62</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1">
+        <v>800</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
@@ -2950,17 +3025,19 @@
         <v>64</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="D29" s="1">
+        <v>1000</v>
+      </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -2968,17 +3045,19 @@
         <v>66</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1">
+        <v>900</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
@@ -2986,17 +3065,19 @@
         <v>68</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1">
+        <v>1100</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>69</v>
       </c>
@@ -3004,17 +3085,19 @@
         <v>70</v>
       </c>
       <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1">
+        <v>800</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,17 +3105,19 @@
         <v>72</v>
       </c>
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1">
+        <v>1000</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
@@ -3040,17 +3125,19 @@
         <v>74</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <v>1100</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>75</v>
       </c>
@@ -3058,17 +3145,19 @@
         <v>76</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="D35" s="1">
+        <v>1200</v>
+      </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>77</v>
       </c>
@@ -3076,17 +3165,19 @@
         <v>78</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="D36" s="1">
+        <v>1000</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
@@ -3094,17 +3185,19 @@
         <v>80</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1">
+        <v>1200</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>81</v>
       </c>
@@ -3112,17 +3205,19 @@
         <v>82</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="D38" s="1">
+        <v>1500</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>83</v>
       </c>
@@ -3130,17 +3225,19 @@
         <v>84</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="D39" s="1">
+        <v>1000</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>85</v>
       </c>
@@ -3148,17 +3245,19 @@
         <v>86</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="D40" s="1">
+        <v>1200</v>
+      </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>87</v>
       </c>
@@ -3166,17 +3265,19 @@
         <v>88</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="D41" s="1">
+        <v>800</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>89</v>
       </c>
@@ -3184,17 +3285,19 @@
         <v>90</v>
       </c>
       <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+      <c r="D42" s="1">
+        <v>1000</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>91</v>
       </c>
@@ -3202,17 +3305,19 @@
         <v>92</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+      <c r="D43" s="1">
+        <v>1500</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>93</v>
       </c>
@@ -3220,17 +3325,19 @@
         <v>94</v>
       </c>
       <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
+      <c r="D44" s="1">
+        <v>1600</v>
+      </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>95</v>
       </c>
@@ -3238,17 +3345,19 @@
         <v>96</v>
       </c>
       <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="D45" s="1">
+        <v>1400</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>97</v>
       </c>
@@ -3256,17 +3365,19 @@
         <v>98</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="D46" s="1">
+        <v>2500</v>
+      </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>99</v>
       </c>
@@ -3274,17 +3385,19 @@
         <v>100</v>
       </c>
       <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="D47" s="1">
+        <v>1100</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>101</v>
       </c>
@@ -3292,17 +3405,19 @@
         <v>102</v>
       </c>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="D48" s="1">
+        <v>2000</v>
+      </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>103</v>
       </c>
@@ -3310,17 +3425,19 @@
         <v>104</v>
       </c>
       <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="D49" s="1">
+        <v>2100</v>
+      </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>105</v>
       </c>
@@ -3328,17 +3445,19 @@
         <v>106</v>
       </c>
       <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+      <c r="D50" s="1">
+        <v>3000</v>
+      </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>107</v>
       </c>
@@ -3346,17 +3465,19 @@
         <v>108</v>
       </c>
       <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+      <c r="D51" s="1">
+        <v>2500</v>
+      </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>109</v>
       </c>
@@ -3364,17 +3485,19 @@
         <v>110</v>
       </c>
       <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+      <c r="D52" s="1">
+        <v>3200</v>
+      </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>111</v>
       </c>
@@ -3382,17 +3505,19 @@
         <v>112</v>
       </c>
       <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="D53" s="1">
+        <v>2600</v>
+      </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>113</v>
       </c>
@@ -3400,17 +3525,19 @@
         <v>114</v>
       </c>
       <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="D54" s="1">
+        <v>3500</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>115</v>
       </c>
@@ -3418,17 +3545,19 @@
         <v>116</v>
       </c>
       <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+      <c r="D55" s="1">
+        <v>3000</v>
+      </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>117</v>
       </c>
@@ -3436,17 +3565,19 @@
         <v>118</v>
       </c>
       <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="D56" s="1">
+        <v>2600</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>119</v>
       </c>
@@ -3454,17 +3585,19 @@
         <v>120</v>
       </c>
       <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+      <c r="D57" s="1">
+        <v>1200</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>121</v>
       </c>
@@ -3472,17 +3605,19 @@
         <v>122</v>
       </c>
       <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+      <c r="D58" s="1">
+        <v>1600</v>
+      </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>123</v>
       </c>
@@ -3490,17 +3625,19 @@
         <v>124</v>
       </c>
       <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+      <c r="D59" s="1">
+        <v>1500</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>125</v>
       </c>
@@ -3508,17 +3645,19 @@
         <v>126</v>
       </c>
       <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+      <c r="D60" s="1">
+        <v>1900</v>
+      </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>127</v>
       </c>
@@ -3526,17 +3665,19 @@
         <v>128</v>
       </c>
       <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
+      <c r="D61" s="1">
+        <v>1600</v>
+      </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>129</v>
       </c>
@@ -3544,17 +3685,19 @@
         <v>130</v>
       </c>
       <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="D62" s="1">
+        <v>2000</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>131</v>
       </c>
@@ -3562,17 +3705,19 @@
         <v>132</v>
       </c>
       <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+      <c r="D63" s="1">
+        <v>1600</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>133</v>
       </c>
@@ -3580,17 +3725,19 @@
         <v>134</v>
       </c>
       <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+      <c r="D64" s="1">
+        <v>1700</v>
+      </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
@@ -3598,17 +3745,19 @@
         <v>136</v>
       </c>
       <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="D65" s="1">
+        <v>100</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>138</v>
       </c>
@@ -3616,17 +3765,19 @@
         <v>139</v>
       </c>
       <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
+      <c r="D66" s="1">
+        <v>200</v>
+      </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>140</v>
       </c>
@@ -3634,17 +3785,19 @@
         <v>141</v>
       </c>
       <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="D67" s="1">
+        <v>90</v>
+      </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
@@ -3652,17 +3805,19 @@
         <v>143</v>
       </c>
       <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+      <c r="D68" s="1">
+        <v>300</v>
+      </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>144</v>
       </c>
@@ -3670,17 +3825,19 @@
         <v>145</v>
       </c>
       <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="D69" s="1">
+        <v>600</v>
+      </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>146</v>
       </c>
@@ -3688,17 +3845,19 @@
         <v>147</v>
       </c>
       <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
+      <c r="D70" s="1">
+        <v>1000</v>
+      </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>149</v>
       </c>
@@ -3706,17 +3865,19 @@
         <v>150</v>
       </c>
       <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+      <c r="D71" s="1">
+        <v>2000</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>151</v>
       </c>
@@ -3724,17 +3885,19 @@
         <v>152</v>
       </c>
       <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="D72" s="1">
+        <v>1000</v>
+      </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>153</v>
       </c>
@@ -3742,17 +3905,19 @@
         <v>154</v>
       </c>
       <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
+      <c r="D73" s="1">
+        <v>2000</v>
+      </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>155</v>
       </c>
@@ -3760,17 +3925,19 @@
         <v>156</v>
       </c>
       <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
+      <c r="D74" s="1">
+        <v>1700</v>
+      </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>157</v>
       </c>
@@ -3778,17 +3945,19 @@
         <v>158</v>
       </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
+      <c r="D75" s="1">
+        <v>2500</v>
+      </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>159</v>
       </c>
@@ -3796,17 +3965,19 @@
         <v>160</v>
       </c>
       <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
+      <c r="D76" s="1">
+        <v>1800</v>
+      </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>161</v>
       </c>
@@ -3814,17 +3985,19 @@
         <v>162</v>
       </c>
       <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
+      <c r="D77" s="1">
+        <v>2600</v>
+      </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>163</v>
       </c>
@@ -3832,17 +4005,19 @@
         <v>164</v>
       </c>
       <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="D78" s="1">
+        <v>1900</v>
+      </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>165</v>
       </c>
@@ -3850,17 +4025,19 @@
         <v>166</v>
       </c>
       <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
+      <c r="D79" s="1">
+        <v>2700</v>
+      </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>167</v>
       </c>
@@ -3868,17 +4045,19 @@
         <v>168</v>
       </c>
       <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
+      <c r="D80" s="1">
+        <v>1700</v>
+      </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>169</v>
       </c>
@@ -3886,17 +4065,19 @@
         <v>170</v>
       </c>
       <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
+      <c r="D81" s="1">
+        <v>2500</v>
+      </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>171</v>
       </c>
@@ -3904,17 +4085,19 @@
         <v>172</v>
       </c>
       <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
+      <c r="D82" s="1">
+        <v>1800</v>
+      </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>173</v>
       </c>
@@ -3922,17 +4105,19 @@
         <v>174</v>
       </c>
       <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
+      <c r="D83" s="1">
+        <v>2600</v>
+      </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>175</v>
       </c>
@@ -3940,17 +4125,19 @@
         <v>176</v>
       </c>
       <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
+      <c r="D84" s="1">
+        <v>1900</v>
+      </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>177</v>
       </c>
@@ -3958,17 +4145,19 @@
         <v>178</v>
       </c>
       <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
+      <c r="D85" s="1">
+        <v>2700</v>
+      </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>179</v>
       </c>
@@ -3976,17 +4165,19 @@
         <v>180</v>
       </c>
       <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
+      <c r="D86" s="1">
+        <v>2200</v>
+      </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>181</v>
       </c>
@@ -3994,17 +4185,19 @@
         <v>182</v>
       </c>
       <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
+      <c r="D87" s="1">
+        <v>2200</v>
+      </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>183</v>
       </c>
@@ -4012,17 +4205,19 @@
         <v>184</v>
       </c>
       <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
+      <c r="D88" s="1">
+        <v>1700</v>
+      </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>185</v>
       </c>
@@ -4030,17 +4225,19 @@
         <v>186</v>
       </c>
       <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
+      <c r="D89" s="1">
+        <v>1900</v>
+      </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>187</v>
       </c>
@@ -4048,17 +4245,19 @@
         <v>188</v>
       </c>
       <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
+      <c r="D90" s="1">
+        <v>600</v>
+      </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>189</v>
       </c>
@@ -4066,17 +4265,19 @@
         <v>190</v>
       </c>
       <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+      <c r="D91" s="1">
+        <v>900</v>
+      </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>191</v>
       </c>
@@ -4084,17 +4285,19 @@
         <v>192</v>
       </c>
       <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="D92" s="1">
+        <v>700</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>193</v>
       </c>
@@ -4102,17 +4305,19 @@
         <v>194</v>
       </c>
       <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+      <c r="D93" s="1">
+        <v>1000</v>
+      </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>195</v>
       </c>
@@ -4120,17 +4325,19 @@
         <v>196</v>
       </c>
       <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+      <c r="D94" s="1">
+        <v>800</v>
+      </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>197</v>
       </c>
@@ -4138,17 +4345,19 @@
         <v>198</v>
       </c>
       <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+      <c r="D95" s="1">
+        <v>1100</v>
+      </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>199</v>
       </c>
@@ -4156,17 +4365,19 @@
         <v>200</v>
       </c>
       <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
+      <c r="D96" s="1">
+        <v>600</v>
+      </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>201</v>
       </c>
@@ -4174,17 +4385,19 @@
         <v>202</v>
       </c>
       <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+      <c r="D97" s="1">
+        <v>900</v>
+      </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>203</v>
       </c>
@@ -4192,17 +4405,19 @@
         <v>204</v>
       </c>
       <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="D98" s="1">
+        <v>700</v>
+      </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>205</v>
       </c>
@@ -4210,17 +4425,19 @@
         <v>206</v>
       </c>
       <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="D99" s="1">
+        <v>1000</v>
+      </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>207</v>
       </c>
@@ -4228,17 +4445,19 @@
         <v>208</v>
       </c>
       <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="D100" s="1">
+        <v>800</v>
+      </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>209</v>
       </c>
@@ -4246,17 +4465,19 @@
         <v>210</v>
       </c>
       <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="D101" s="1">
+        <v>1100</v>
+      </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>211</v>
       </c>
@@ -4264,17 +4485,19 @@
         <v>212</v>
       </c>
       <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+      <c r="D102" s="1">
+        <v>1000</v>
+      </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>213</v>
       </c>
@@ -4282,17 +4505,19 @@
         <v>214</v>
       </c>
       <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
+      <c r="D103" s="1">
+        <v>1100</v>
+      </c>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>215</v>
       </c>
@@ -4300,17 +4525,19 @@
         <v>216</v>
       </c>
       <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="D104" s="1">
+        <v>1000</v>
+      </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>217</v>
       </c>
@@ -4318,17 +4545,19 @@
         <v>218</v>
       </c>
       <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
+      <c r="D105" s="1">
+        <v>1100</v>
+      </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>219</v>
       </c>
@@ -4336,17 +4565,19 @@
         <v>220</v>
       </c>
       <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
+      <c r="D106" s="1">
+        <v>1500</v>
+      </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>221</v>
       </c>
@@ -4354,17 +4585,19 @@
         <v>222</v>
       </c>
       <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="D107" s="1">
+        <v>2500</v>
+      </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>223</v>
       </c>
@@ -4372,17 +4605,19 @@
         <v>224</v>
       </c>
       <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
+      <c r="D108" s="1">
+        <v>1500</v>
+      </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>225</v>
       </c>
@@ -4390,17 +4625,19 @@
         <v>226</v>
       </c>
       <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
+      <c r="D109" s="1">
+        <v>2500</v>
+      </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>227</v>
       </c>
@@ -4408,17 +4645,19 @@
         <v>228</v>
       </c>
       <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="D110" s="1">
+        <v>2200</v>
+      </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>229</v>
       </c>
@@ -4426,17 +4665,19 @@
         <v>230</v>
       </c>
       <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="D111" s="1">
+        <v>3000</v>
+      </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>231</v>
       </c>
@@ -4444,17 +4685,19 @@
         <v>232</v>
       </c>
       <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
+      <c r="D112" s="1">
+        <v>2400</v>
+      </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>233</v>
       </c>
@@ -4462,17 +4705,19 @@
         <v>234</v>
       </c>
       <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
+      <c r="D113" s="1">
+        <v>3200</v>
+      </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>235</v>
       </c>
@@ -4480,17 +4725,19 @@
         <v>236</v>
       </c>
       <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
+      <c r="D114" s="1">
+        <v>2500</v>
+      </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>237</v>
       </c>
@@ -4498,17 +4745,19 @@
         <v>238</v>
       </c>
       <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
+      <c r="D115" s="1">
+        <v>3500</v>
+      </c>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>239</v>
       </c>
@@ -4516,17 +4765,19 @@
         <v>240</v>
       </c>
       <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="D116" s="1">
+        <v>2200</v>
+      </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>241</v>
       </c>
@@ -4534,17 +4785,19 @@
         <v>242</v>
       </c>
       <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
+      <c r="D117" s="1">
+        <v>3000</v>
+      </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>243</v>
       </c>
@@ -4552,17 +4805,19 @@
         <v>244</v>
       </c>
       <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="D118" s="1">
+        <v>2400</v>
+      </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>245</v>
       </c>
@@ -4570,17 +4825,19 @@
         <v>246</v>
       </c>
       <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="D119" s="1">
+        <v>3200</v>
+      </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>247</v>
       </c>
@@ -4588,17 +4845,19 @@
         <v>248</v>
       </c>
       <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="D120" s="1">
+        <v>2500</v>
+      </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>249</v>
       </c>
@@ -4606,17 +4865,19 @@
         <v>250</v>
       </c>
       <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="D121" s="1">
+        <v>3500</v>
+      </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>251</v>
       </c>
@@ -4624,17 +4885,19 @@
         <v>252</v>
       </c>
       <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="D122" s="1">
+        <v>3000</v>
+      </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>253</v>
       </c>
@@ -4642,17 +4905,19 @@
         <v>254</v>
       </c>
       <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="D123" s="1">
+        <v>3000</v>
+      </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>255</v>
       </c>
@@ -4660,17 +4925,19 @@
         <v>256</v>
       </c>
       <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="D124" s="1">
+        <v>2500</v>
+      </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>257</v>
       </c>
@@ -4678,17 +4945,19 @@
         <v>258</v>
       </c>
       <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="D125" s="1">
+        <v>2600</v>
+      </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>259</v>
       </c>
@@ -4696,17 +4965,19 @@
         <v>260</v>
       </c>
       <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="D126" s="1">
+        <v>1300</v>
+      </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>261</v>
       </c>
@@ -4714,17 +4985,19 @@
         <v>262</v>
       </c>
       <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="D127" s="1">
+        <v>1600</v>
+      </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>263</v>
       </c>
@@ -4732,17 +5005,19 @@
         <v>264</v>
       </c>
       <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="D128" s="1">
+        <v>1500</v>
+      </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>265</v>
       </c>
@@ -4750,17 +5025,19 @@
         <v>266</v>
       </c>
       <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="D129" s="1">
+        <v>1800</v>
+      </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>267</v>
       </c>
@@ -4768,17 +5045,19 @@
         <v>268</v>
       </c>
       <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="D130" s="1">
+        <v>1700</v>
+      </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>269</v>
       </c>
@@ -4786,17 +5065,19 @@
         <v>270</v>
       </c>
       <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="D131" s="1">
+        <v>2000</v>
+      </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>271</v>
       </c>
@@ -4804,3921 +5085,3979 @@
         <v>272</v>
       </c>
       <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="D132" s="1">
+        <v>1300</v>
+      </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>273</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>274</v>
+        <v>703</v>
       </c>
       <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="D133" s="1">
+        <v>1600</v>
+      </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>276</v>
+        <v>704</v>
       </c>
       <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="D134" s="1">
+        <v>1500</v>
+      </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>278</v>
+        <v>705</v>
       </c>
       <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="D135" s="1">
+        <v>1800</v>
+      </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>280</v>
+        <v>706</v>
       </c>
       <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="D136" s="1">
+        <v>1700</v>
+      </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>282</v>
+        <v>702</v>
       </c>
       <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="D137" s="1">
+        <v>2000</v>
+      </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>284</v>
+        <v>707</v>
       </c>
       <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="D138" s="1">
+        <v>1800</v>
+      </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>286</v>
+        <v>708</v>
       </c>
       <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="D139" s="1">
+        <v>1800</v>
+      </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>288</v>
+        <v>709</v>
       </c>
       <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="D140" s="1">
+        <v>1800</v>
+      </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="D141" s="1">
+        <v>1800</v>
+      </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C142" s="4" t="str">
-        <f>Hancolor!H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D142" s="1"/>
+        <v>284</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="1">
+        <v>21000</v>
+      </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="D143" s="1">
+        <v>19500</v>
+      </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C144" s="4" t="str">
-        <f>Hancolor!H17</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D144" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="C144" s="4"/>
+      <c r="D144" s="1">
+        <v>22000</v>
+      </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C145" s="4" t="str">
-        <f>Hancolor!H20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D145" s="1"/>
+        <v>291</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="1">
+        <v>23000</v>
+      </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H145" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C146" s="3">
-        <v>3500.0</v>
-      </c>
-      <c r="D146" s="1"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="1">
+        <v>3500</v>
+      </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C147" s="3">
-        <v>4500.0</v>
-      </c>
-      <c r="D147" s="1"/>
+        <v>295</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="1">
+        <v>3500</v>
+      </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C148" s="5" t="str">
-        <f t="shared" ref="C148:C149" si="1">Hancolor!H11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D148" s="1"/>
+        <v>297</v>
+      </c>
+      <c r="C148" s="5"/>
+      <c r="D148" s="1">
+        <v>23700</v>
+      </c>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C149" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="D149" s="1"/>
+        <v>299</v>
+      </c>
+      <c r="C149" s="5"/>
+      <c r="D149" s="1">
+        <v>28900</v>
+      </c>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="150">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C150" s="4" t="str">
-        <f>Hancolor!H35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D150" s="1"/>
+        <v>301</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="1">
+        <v>26000</v>
+      </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="151">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C151" s="4" t="str">
-        <f>Hancolor!H14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D151" s="1"/>
+        <v>303</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="1">
+        <v>22000</v>
+      </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C152" s="4" t="str">
-        <f>Hancolor!H23</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D152" s="1"/>
+        <v>306</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="1">
+        <v>28000</v>
+      </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="153">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C153" s="4" t="str">
-        <f>Hancolor!H29</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D153" s="1"/>
+        <v>308</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="1">
+        <v>28000</v>
+      </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C154" s="4" t="str">
-        <f>Hancolor!H26</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D154" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="1">
+        <v>28000</v>
+      </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>320</v>
+        <v>710</v>
       </c>
       <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="D155" s="1">
+        <v>18000</v>
+      </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="156">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>323</v>
+        <v>711</v>
       </c>
       <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="D156" s="1">
+        <v>20000</v>
+      </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>325</v>
+        <v>712</v>
       </c>
       <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="D157" s="1">
+        <v>20000</v>
+      </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>327</v>
+        <v>713</v>
       </c>
       <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="D158" s="1">
+        <v>20000</v>
+      </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="159">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="D159" s="1">
+        <v>1000</v>
+      </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="D160" s="1">
+        <v>1100</v>
+      </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="D161" s="1">
+        <v>1100</v>
+      </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="D162" s="1">
+        <v>8200</v>
+      </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="163">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="D163" s="1">
+        <v>12500</v>
+      </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="164">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="D164" s="1">
+        <v>12500</v>
+      </c>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="D165" s="1">
+        <v>12500</v>
+      </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="166">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="D166" s="1">
+        <v>9500</v>
+      </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="D167" s="1">
+        <v>12000</v>
+      </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H167" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="D168" s="1">
+        <v>55000</v>
+      </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="169">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="D169" s="1">
+        <v>70000</v>
+      </c>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="170">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="D170" s="1">
+        <v>93000</v>
+      </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="171">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="D171" s="1">
+        <v>98000</v>
+      </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="D172" s="1">
+        <v>85000</v>
+      </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="D173" s="1">
+        <v>4500</v>
+      </c>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="D174" s="1">
+        <v>1500</v>
+      </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="175">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="D175" s="1">
+        <v>12500</v>
+      </c>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="D176" s="1">
+        <v>19200</v>
+      </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="D177" s="1">
+        <v>29000</v>
+      </c>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="178">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H178" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>360</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="183">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="185">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="186">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="187">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="188">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="189">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="190">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="191">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H191" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A192" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>388</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="194">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="195">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="196">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="199">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="200">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H200" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A201" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="203">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="204">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="206">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="207">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
       <c r="G207" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
       <c r="G208" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="210">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
       <c r="G210" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="214">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H215" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A216" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>438</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="217">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="219">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H223" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A224" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>456</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="227">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="229">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="230">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="231">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="232">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="233">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="234">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="236">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="240">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="241">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="243">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="244">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="245">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="246">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="247">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="248">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="249">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="250">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="251">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="252">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="253">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="254">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="255">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="256">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="257">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="258">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="259">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="260">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H260" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A261" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>532</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="262">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="263">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="264">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="265">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="266">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="267">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="268">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="269">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="270">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="271">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="272">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="273">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="274">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H274" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A275" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>561</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="276">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="277">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="278">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="279">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="280">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="281">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="282">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="283">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="284">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="285">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="286">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="287">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="288">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="289">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="290">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="291">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="292">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="293">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="294">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="295">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="296">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="297">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="298">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="299">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="300">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="301">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="302">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="303">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="304">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="305">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="306">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="307">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="308">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="309">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="310">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="311">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="312">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H312" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A313" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>638</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>650</v>
       </c>
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="314">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="315">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="316">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="317">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="318">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="319">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="320">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="321">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="322">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="323">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="324">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="325">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="326">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="327">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="328">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="329">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="330">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="331">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="332">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="333">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="334">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="335">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="336">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="337">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="338">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="339">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="340">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="341">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="342">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="343">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="344">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="345">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H345" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A346" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>699</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="347">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="3">
-        <v>9999.0</v>
+        <v>9999</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/Precios final.xlsx
+++ b/src/Precios final.xlsx
@@ -2448,7 +2448,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="1.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2477,7 +2478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2497,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -2577,7 +2578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -2717,7 +2718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -2777,7 +2778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -6005,7 +6006,9 @@
         <v>358</v>
       </c>
       <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="D178" s="1">
+        <v>12000</v>
+      </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="3">
@@ -6077,7 +6080,9 @@
         <v>366</v>
       </c>
       <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="D182" s="1">
+        <v>19000</v>
+      </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="3">
@@ -6095,7 +6100,9 @@
         <v>369</v>
       </c>
       <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="D183" s="1">
+        <v>30000</v>
+      </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="3">
@@ -6113,7 +6120,9 @@
         <v>371</v>
       </c>
       <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="D184" s="1">
+        <v>9000</v>
+      </c>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="3">
@@ -6131,7 +6140,9 @@
         <v>373</v>
       </c>
       <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="D185" s="1">
+        <v>20000</v>
+      </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="3">
@@ -6149,7 +6160,9 @@
         <v>375</v>
       </c>
       <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="D186" s="1">
+        <v>1000</v>
+      </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="3">
@@ -6167,7 +6180,9 @@
         <v>378</v>
       </c>
       <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="D187" s="1">
+        <v>1500</v>
+      </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="3">
@@ -6185,7 +6200,9 @@
         <v>380</v>
       </c>
       <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="D188" s="1">
+        <v>2000</v>
+      </c>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="3">
@@ -6203,7 +6220,9 @@
         <v>382</v>
       </c>
       <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="D189" s="1">
+        <v>2500</v>
+      </c>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="3">
@@ -6221,7 +6240,9 @@
         <v>384</v>
       </c>
       <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="D190" s="1">
+        <v>1000</v>
+      </c>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="3">
@@ -6239,7 +6260,9 @@
         <v>386</v>
       </c>
       <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="D191" s="1">
+        <v>1200</v>
+      </c>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="3">
@@ -6257,7 +6280,9 @@
         <v>388</v>
       </c>
       <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="D192" s="1">
+        <v>1500</v>
+      </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="3">
@@ -6275,7 +6300,9 @@
         <v>390</v>
       </c>
       <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="D193" s="1">
+        <v>2500</v>
+      </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="3">
@@ -6293,7 +6320,9 @@
         <v>392</v>
       </c>
       <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="D194" s="1">
+        <v>6000</v>
+      </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="3">
@@ -6311,7 +6340,9 @@
         <v>394</v>
       </c>
       <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="D195" s="1">
+        <v>7000</v>
+      </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="3">
@@ -6329,7 +6360,9 @@
         <v>397</v>
       </c>
       <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="D196" s="1">
+        <v>7000</v>
+      </c>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="3">
@@ -6347,7 +6380,9 @@
         <v>399</v>
       </c>
       <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="D197" s="1">
+        <v>7500</v>
+      </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="3">
@@ -6365,7 +6400,9 @@
         <v>401</v>
       </c>
       <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="D198" s="1">
+        <v>4000</v>
+      </c>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="3">
@@ -6383,7 +6420,9 @@
         <v>403</v>
       </c>
       <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="D199" s="1">
+        <v>10000</v>
+      </c>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="3">
@@ -6401,7 +6440,9 @@
         <v>405</v>
       </c>
       <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="D200" s="1">
+        <v>10000</v>
+      </c>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="3">
@@ -6419,7 +6460,9 @@
         <v>407</v>
       </c>
       <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="D201" s="1">
+        <v>16000</v>
+      </c>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="3">
@@ -6437,7 +6480,9 @@
         <v>409</v>
       </c>
       <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="D202" s="1">
+        <v>21000</v>
+      </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="3">
@@ -6455,7 +6500,9 @@
         <v>411</v>
       </c>
       <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="D203" s="1">
+        <v>1000</v>
+      </c>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="3">
@@ -6473,7 +6520,9 @@
         <v>413</v>
       </c>
       <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="D204" s="1">
+        <v>1500</v>
+      </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="3">
@@ -6491,7 +6540,9 @@
         <v>415</v>
       </c>
       <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="D205" s="1">
+        <v>1700</v>
+      </c>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="3">
@@ -6509,7 +6560,9 @@
         <v>417</v>
       </c>
       <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="D206" s="1">
+        <v>2000</v>
+      </c>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="3">
@@ -6527,7 +6580,9 @@
         <v>419</v>
       </c>
       <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="D207" s="1">
+        <v>2200</v>
+      </c>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
       <c r="G207" s="3">
@@ -6545,7 +6600,9 @@
         <v>421</v>
       </c>
       <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="D208" s="1">
+        <v>1500</v>
+      </c>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
       <c r="G208" s="3">
@@ -6563,7 +6620,9 @@
         <v>423</v>
       </c>
       <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="D209" s="1">
+        <v>2500</v>
+      </c>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="3">
@@ -6581,7 +6640,9 @@
         <v>425</v>
       </c>
       <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="D210" s="1">
+        <v>1400</v>
+      </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
       <c r="G210" s="3">
@@ -6599,7 +6660,9 @@
         <v>428</v>
       </c>
       <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="D211" s="1">
+        <v>1100</v>
+      </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="3">
@@ -6617,7 +6680,9 @@
         <v>430</v>
       </c>
       <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="D212" s="1">
+        <v>900</v>
+      </c>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="3">
@@ -6635,7 +6700,9 @@
         <v>432</v>
       </c>
       <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="D213" s="1">
+        <v>2100</v>
+      </c>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="3">
@@ -6653,7 +6720,9 @@
         <v>434</v>
       </c>
       <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="D214" s="1">
+        <v>1700</v>
+      </c>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="3">
@@ -6671,7 +6740,9 @@
         <v>436</v>
       </c>
       <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="D215" s="1">
+        <v>2000</v>
+      </c>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="3">
@@ -6689,7 +6760,9 @@
         <v>438</v>
       </c>
       <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="D216" s="1">
+        <v>10000</v>
+      </c>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="3">
@@ -6707,7 +6780,9 @@
         <v>441</v>
       </c>
       <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="D217" s="1">
+        <v>10000</v>
+      </c>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="3">
@@ -6725,7 +6800,9 @@
         <v>443</v>
       </c>
       <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="D218" s="1">
+        <v>8500</v>
+      </c>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="3">
@@ -6743,7 +6820,9 @@
         <v>446</v>
       </c>
       <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="D219" s="1">
+        <v>9500</v>
+      </c>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="3">
@@ -6761,7 +6840,9 @@
         <v>448</v>
       </c>
       <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="D220" s="1">
+        <v>20</v>
+      </c>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="3">
@@ -6779,7 +6860,9 @@
         <v>450</v>
       </c>
       <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="D221" s="1">
+        <v>50</v>
+      </c>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="3">
@@ -6797,7 +6880,9 @@
         <v>452</v>
       </c>
       <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="D222" s="1">
+        <v>150</v>
+      </c>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="3">
@@ -6815,7 +6900,9 @@
         <v>454</v>
       </c>
       <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="D223" s="1">
+        <v>300</v>
+      </c>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="3">
@@ -6833,7 +6920,9 @@
         <v>456</v>
       </c>
       <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="D224" s="1">
+        <v>350</v>
+      </c>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="3">
@@ -6851,7 +6940,9 @@
         <v>458</v>
       </c>
       <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="D225" s="1">
+        <v>250</v>
+      </c>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="3">
@@ -6869,7 +6960,9 @@
         <v>460</v>
       </c>
       <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="D226" s="1">
+        <v>400</v>
+      </c>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="3">
@@ -6887,7 +6980,9 @@
         <v>462</v>
       </c>
       <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="D227" s="1">
+        <v>500</v>
+      </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="3">
@@ -6905,7 +7000,9 @@
         <v>464</v>
       </c>
       <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="D228" s="1">
+        <v>220</v>
+      </c>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="3">
@@ -6923,7 +7020,9 @@
         <v>466</v>
       </c>
       <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="D229" s="1">
+        <v>350</v>
+      </c>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="3">
@@ -6941,7 +7040,9 @@
         <v>468</v>
       </c>
       <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="D230" s="1">
+        <v>500</v>
+      </c>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="3">
@@ -6959,7 +7060,9 @@
         <v>470</v>
       </c>
       <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="D231" s="1">
+        <v>400</v>
+      </c>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="3">
@@ -6977,7 +7080,9 @@
         <v>472</v>
       </c>
       <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="D232" s="1">
+        <v>300</v>
+      </c>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="3">
@@ -6995,7 +7100,9 @@
         <v>474</v>
       </c>
       <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="D233" s="1">
+        <v>250</v>
+      </c>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="3">
@@ -7013,7 +7120,9 @@
         <v>476</v>
       </c>
       <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="D234" s="1">
+        <v>6500</v>
+      </c>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="3">
@@ -7031,7 +7140,9 @@
         <v>478</v>
       </c>
       <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="D235" s="1">
+        <v>1000</v>
+      </c>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="3">
@@ -7049,7 +7160,9 @@
         <v>480</v>
       </c>
       <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="D236" s="1">
+        <v>300</v>
+      </c>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="3">
@@ -7067,7 +7180,9 @@
         <v>482</v>
       </c>
       <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="D237" s="1">
+        <v>400</v>
+      </c>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="3">
@@ -7085,7 +7200,9 @@
         <v>484</v>
       </c>
       <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="D238" s="1">
+        <v>500</v>
+      </c>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="3">
@@ -7103,7 +7220,9 @@
         <v>486</v>
       </c>
       <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="D239" s="1">
+        <v>400</v>
+      </c>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="3">
@@ -7121,7 +7240,9 @@
         <v>488</v>
       </c>
       <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="D240" s="1">
+        <v>420</v>
+      </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="3">
@@ -7139,7 +7260,9 @@
         <v>490</v>
       </c>
       <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
+      <c r="D241" s="1">
+        <v>450</v>
+      </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="3">
@@ -7157,7 +7280,9 @@
         <v>492</v>
       </c>
       <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
+      <c r="D242" s="1">
+        <v>680</v>
+      </c>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="3">
@@ -7175,7 +7300,9 @@
         <v>494</v>
       </c>
       <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
+      <c r="D243" s="1">
+        <v>200</v>
+      </c>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="3">
@@ -7193,7 +7320,9 @@
         <v>496</v>
       </c>
       <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
+      <c r="D244" s="1">
+        <v>200</v>
+      </c>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="3">
@@ -7211,7 +7340,9 @@
         <v>498</v>
       </c>
       <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
+      <c r="D245" s="1">
+        <v>400</v>
+      </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="3">
@@ -7229,7 +7360,9 @@
         <v>500</v>
       </c>
       <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
+      <c r="D246" s="1">
+        <v>300</v>
+      </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="3">
@@ -7247,7 +7380,9 @@
         <v>502</v>
       </c>
       <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
+      <c r="D247" s="1">
+        <v>500</v>
+      </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="3">
@@ -7265,7 +7400,9 @@
         <v>504</v>
       </c>
       <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
+      <c r="D248" s="1">
+        <v>5000</v>
+      </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="3">
@@ -7283,7 +7420,9 @@
         <v>506</v>
       </c>
       <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
+      <c r="D249" s="1">
+        <v>16000</v>
+      </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="3">
@@ -7301,7 +7440,9 @@
         <v>508</v>
       </c>
       <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
+      <c r="D250" s="1">
+        <v>35000</v>
+      </c>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="3">
@@ -7319,7 +7460,9 @@
         <v>510</v>
       </c>
       <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
+      <c r="D251" s="1">
+        <v>15000</v>
+      </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="3">
@@ -7337,7 +7480,9 @@
         <v>513</v>
       </c>
       <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
+      <c r="D252" s="1">
+        <v>15000</v>
+      </c>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="3">
@@ -7355,7 +7500,9 @@
         <v>515</v>
       </c>
       <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
+      <c r="D253" s="1">
+        <v>15000</v>
+      </c>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="3">
@@ -7373,7 +7520,9 @@
         <v>517</v>
       </c>
       <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
+      <c r="D254" s="1">
+        <v>15000</v>
+      </c>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="3">
@@ -7391,7 +7540,9 @@
         <v>519</v>
       </c>
       <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
+      <c r="D255" s="1">
+        <v>10000</v>
+      </c>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="3">
@@ -7409,7 +7560,9 @@
         <v>522</v>
       </c>
       <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
+      <c r="D256" s="1">
+        <v>2500</v>
+      </c>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="3">
@@ -7427,7 +7580,9 @@
         <v>524</v>
       </c>
       <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
+      <c r="D257" s="1">
+        <v>25000</v>
+      </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="3">
@@ -7445,7 +7600,9 @@
         <v>526</v>
       </c>
       <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
+      <c r="D258" s="1">
+        <v>15000</v>
+      </c>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="3">
@@ -7463,7 +7620,9 @@
         <v>528</v>
       </c>
       <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
+      <c r="D259" s="1">
+        <v>10000</v>
+      </c>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="3">
@@ -7481,7 +7640,9 @@
         <v>530</v>
       </c>
       <c r="C260" s="1"/>
-      <c r="D260" s="1"/>
+      <c r="D260" s="1">
+        <v>7000</v>
+      </c>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="3">
@@ -7499,7 +7660,9 @@
         <v>532</v>
       </c>
       <c r="C261" s="1"/>
-      <c r="D261" s="1"/>
+      <c r="D261" s="1">
+        <v>12000</v>
+      </c>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="3">
@@ -7517,7 +7680,9 @@
         <v>534</v>
       </c>
       <c r="C262" s="1"/>
-      <c r="D262" s="1"/>
+      <c r="D262" s="1">
+        <v>45000</v>
+      </c>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="3">
@@ -7535,7 +7700,9 @@
         <v>536</v>
       </c>
       <c r="C263" s="1"/>
-      <c r="D263" s="1"/>
+      <c r="D263" s="1">
+        <v>60000</v>
+      </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="3">
@@ -7553,7 +7720,9 @@
         <v>538</v>
       </c>
       <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
+      <c r="D264" s="1">
+        <v>25000</v>
+      </c>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="3">
@@ -7571,7 +7740,9 @@
         <v>540</v>
       </c>
       <c r="C265" s="1"/>
-      <c r="D265" s="1"/>
+      <c r="D265" s="1">
+        <v>10000</v>
+      </c>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="3">
@@ -7589,7 +7760,9 @@
         <v>542</v>
       </c>
       <c r="C266" s="1"/>
-      <c r="D266" s="1"/>
+      <c r="D266" s="1">
+        <v>10000</v>
+      </c>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="3">
@@ -7607,7 +7780,9 @@
         <v>544</v>
       </c>
       <c r="C267" s="1"/>
-      <c r="D267" s="1"/>
+      <c r="D267" s="1">
+        <v>15000</v>
+      </c>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="3">
@@ -7625,7 +7800,9 @@
         <v>546</v>
       </c>
       <c r="C268" s="1"/>
-      <c r="D268" s="1"/>
+      <c r="D268" s="1">
+        <v>15000</v>
+      </c>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="3">
@@ -7643,7 +7820,9 @@
         <v>548</v>
       </c>
       <c r="C269" s="1"/>
-      <c r="D269" s="1"/>
+      <c r="D269" s="1">
+        <v>15800</v>
+      </c>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="3">
@@ -7661,7 +7840,9 @@
         <v>551</v>
       </c>
       <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
+      <c r="D270" s="1">
+        <v>20300</v>
+      </c>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="3">
@@ -7679,7 +7860,9 @@
         <v>553</v>
       </c>
       <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
+      <c r="D271" s="1">
+        <v>36200</v>
+      </c>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="3">
@@ -7697,7 +7880,9 @@
         <v>555</v>
       </c>
       <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
+      <c r="D272" s="1">
+        <v>43900</v>
+      </c>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="3">
@@ -7715,7 +7900,9 @@
         <v>557</v>
       </c>
       <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
+      <c r="D273" s="1">
+        <v>51600</v>
+      </c>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="3">
@@ -7733,7 +7920,9 @@
         <v>559</v>
       </c>
       <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
+      <c r="D274" s="1">
+        <v>55000</v>
+      </c>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="3">
@@ -7751,7 +7940,9 @@
         <v>561</v>
       </c>
       <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
+      <c r="D275" s="1">
+        <v>58000</v>
+      </c>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="3">
@@ -7769,7 +7960,9 @@
         <v>563</v>
       </c>
       <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
+      <c r="D276" s="1">
+        <v>59300</v>
+      </c>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="3">
@@ -7787,7 +7980,9 @@
         <v>565</v>
       </c>
       <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
+      <c r="D277" s="1">
+        <v>62700</v>
+      </c>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="3">
@@ -7805,7 +8000,9 @@
         <v>567</v>
       </c>
       <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
+      <c r="D278" s="1">
+        <v>67000</v>
+      </c>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="3">
@@ -7823,7 +8020,9 @@
         <v>569</v>
       </c>
       <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
+      <c r="D279" s="1">
+        <v>95000</v>
+      </c>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="3">
@@ -7841,7 +8040,9 @@
         <v>571</v>
       </c>
       <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
+      <c r="D280" s="1">
+        <v>17000</v>
+      </c>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="3">
@@ -7859,7 +8060,9 @@
         <v>573</v>
       </c>
       <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+      <c r="D281" s="1">
+        <v>25000</v>
+      </c>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="3">
@@ -7877,7 +8080,9 @@
         <v>575</v>
       </c>
       <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
+      <c r="D282" s="1">
+        <v>35000</v>
+      </c>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="3">
@@ -7895,7 +8100,9 @@
         <v>577</v>
       </c>
       <c r="C283" s="1"/>
-      <c r="D283" s="1"/>
+      <c r="D283" s="1">
+        <v>41000</v>
+      </c>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="3">
@@ -7913,7 +8120,9 @@
         <v>579</v>
       </c>
       <c r="C284" s="1"/>
-      <c r="D284" s="1"/>
+      <c r="D284" s="1">
+        <v>50000</v>
+      </c>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="3">
@@ -7931,7 +8140,9 @@
         <v>581</v>
       </c>
       <c r="C285" s="1"/>
-      <c r="D285" s="1"/>
+      <c r="D285" s="1">
+        <v>58000</v>
+      </c>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="3">
@@ -7949,7 +8160,9 @@
         <v>583</v>
       </c>
       <c r="C286" s="1"/>
-      <c r="D286" s="1"/>
+      <c r="D286" s="1">
+        <v>65000</v>
+      </c>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="3">
@@ -7967,7 +8180,9 @@
         <v>585</v>
       </c>
       <c r="C287" s="1"/>
-      <c r="D287" s="1"/>
+      <c r="D287" s="1">
+        <v>72000</v>
+      </c>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="3">
@@ -7985,7 +8200,9 @@
         <v>587</v>
       </c>
       <c r="C288" s="1"/>
-      <c r="D288" s="1"/>
+      <c r="D288" s="1">
+        <v>78000</v>
+      </c>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="3">
@@ -8003,7 +8220,9 @@
         <v>589</v>
       </c>
       <c r="C289" s="1"/>
-      <c r="D289" s="1"/>
+      <c r="D289" s="1">
+        <v>85000</v>
+      </c>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="3">
@@ -8021,7 +8240,9 @@
         <v>591</v>
       </c>
       <c r="C290" s="1"/>
-      <c r="D290" s="1"/>
+      <c r="D290" s="1">
+        <v>120000</v>
+      </c>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="3">
@@ -8039,7 +8260,9 @@
         <v>593</v>
       </c>
       <c r="C291" s="1"/>
-      <c r="D291" s="1"/>
+      <c r="D291" s="1">
+        <v>24000</v>
+      </c>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="3">
@@ -8057,7 +8280,9 @@
         <v>595</v>
       </c>
       <c r="C292" s="1"/>
-      <c r="D292" s="1"/>
+      <c r="D292" s="1">
+        <v>35000</v>
+      </c>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="3">
@@ -8075,7 +8300,9 @@
         <v>597</v>
       </c>
       <c r="C293" s="1"/>
-      <c r="D293" s="1"/>
+      <c r="D293" s="1">
+        <v>49000</v>
+      </c>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="3">
@@ -8093,7 +8320,9 @@
         <v>599</v>
       </c>
       <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
+      <c r="D294" s="1">
+        <v>57000</v>
+      </c>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="3">
@@ -8111,7 +8340,9 @@
         <v>601</v>
       </c>
       <c r="C295" s="1"/>
-      <c r="D295" s="1"/>
+      <c r="D295" s="1">
+        <v>70000</v>
+      </c>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="3">
@@ -8129,7 +8360,9 @@
         <v>603</v>
       </c>
       <c r="C296" s="1"/>
-      <c r="D296" s="1"/>
+      <c r="D296" s="1">
+        <v>81000</v>
+      </c>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="3">
@@ -8147,7 +8380,9 @@
         <v>605</v>
       </c>
       <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
+      <c r="D297" s="1">
+        <v>90000</v>
+      </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="3">
@@ -8165,7 +8400,9 @@
         <v>607</v>
       </c>
       <c r="C298" s="1"/>
-      <c r="D298" s="1"/>
+      <c r="D298" s="1">
+        <v>100000</v>
+      </c>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="3">
@@ -8183,7 +8420,9 @@
         <v>609</v>
       </c>
       <c r="C299" s="1"/>
-      <c r="D299" s="1"/>
+      <c r="D299" s="1">
+        <v>110000</v>
+      </c>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="3">
@@ -8201,7 +8440,9 @@
         <v>611</v>
       </c>
       <c r="C300" s="1"/>
-      <c r="D300" s="1"/>
+      <c r="D300" s="1">
+        <v>120000</v>
+      </c>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="3">
@@ -8219,7 +8460,9 @@
         <v>613</v>
       </c>
       <c r="C301" s="1"/>
-      <c r="D301" s="1"/>
+      <c r="D301" s="1">
+        <v>165000</v>
+      </c>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="3">
@@ -8237,7 +8480,9 @@
         <v>615</v>
       </c>
       <c r="C302" s="1"/>
-      <c r="D302" s="1"/>
+      <c r="D302" s="1">
+        <v>15800</v>
+      </c>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="3">
@@ -8255,7 +8500,9 @@
         <v>617</v>
       </c>
       <c r="C303" s="1"/>
-      <c r="D303" s="1"/>
+      <c r="D303" s="1">
+        <v>20300</v>
+      </c>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="3">
@@ -8273,7 +8520,9 @@
         <v>619</v>
       </c>
       <c r="C304" s="1"/>
-      <c r="D304" s="1"/>
+      <c r="D304" s="1">
+        <v>36200</v>
+      </c>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="3">
@@ -8291,7 +8540,9 @@
         <v>621</v>
       </c>
       <c r="C305" s="1"/>
-      <c r="D305" s="1"/>
+      <c r="D305" s="1">
+        <v>43900</v>
+      </c>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="3">
@@ -8309,7 +8560,9 @@
         <v>623</v>
       </c>
       <c r="C306" s="1"/>
-      <c r="D306" s="1"/>
+      <c r="D306" s="1">
+        <v>51600</v>
+      </c>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="3">
@@ -8327,7 +8580,9 @@
         <v>625</v>
       </c>
       <c r="C307" s="1"/>
-      <c r="D307" s="1"/>
+      <c r="D307" s="1">
+        <v>3000</v>
+      </c>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="3">
@@ -8345,7 +8600,9 @@
         <v>628</v>
       </c>
       <c r="C308" s="1"/>
-      <c r="D308" s="1"/>
+      <c r="D308" s="1">
+        <v>6500</v>
+      </c>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="3">
@@ -8363,7 +8620,9 @@
         <v>630</v>
       </c>
       <c r="C309" s="1"/>
-      <c r="D309" s="1"/>
+      <c r="D309" s="1">
+        <v>10500</v>
+      </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="3">
@@ -8381,7 +8640,9 @@
         <v>632</v>
       </c>
       <c r="C310" s="1"/>
-      <c r="D310" s="1"/>
+      <c r="D310" s="1">
+        <v>18750</v>
+      </c>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="3">
@@ -8399,7 +8660,9 @@
         <v>634</v>
       </c>
       <c r="C311" s="1"/>
-      <c r="D311" s="1"/>
+      <c r="D311" s="1">
+        <v>75000</v>
+      </c>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="3">
@@ -8417,7 +8680,9 @@
         <v>636</v>
       </c>
       <c r="C312" s="1"/>
-      <c r="D312" s="1"/>
+      <c r="D312" s="1">
+        <v>5000</v>
+      </c>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="3">
@@ -8435,7 +8700,9 @@
         <v>638</v>
       </c>
       <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
+      <c r="D313" s="1">
+        <v>10500</v>
+      </c>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="3">
@@ -8453,7 +8720,9 @@
         <v>640</v>
       </c>
       <c r="C314" s="1"/>
-      <c r="D314" s="1"/>
+      <c r="D314" s="1">
+        <v>18750</v>
+      </c>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="3">
@@ -8471,7 +8740,9 @@
         <v>642</v>
       </c>
       <c r="C315" s="1"/>
-      <c r="D315" s="1"/>
+      <c r="D315" s="1">
+        <v>36000</v>
+      </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="3">
@@ -8489,7 +8760,9 @@
         <v>644</v>
       </c>
       <c r="C316" s="1"/>
-      <c r="D316" s="1"/>
+      <c r="D316" s="1">
+        <v>137000</v>
+      </c>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="3">
@@ -8741,7 +9014,9 @@
         <v>672</v>
       </c>
       <c r="C330" s="1"/>
-      <c r="D330" s="1"/>
+      <c r="D330" s="1">
+        <v>7000</v>
+      </c>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="3">
@@ -8813,7 +9088,9 @@
         <v>677</v>
       </c>
       <c r="C334" s="1"/>
-      <c r="D334" s="1"/>
+      <c r="D334" s="1">
+        <v>2500</v>
+      </c>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="3">
@@ -8831,7 +9108,9 @@
         <v>679</v>
       </c>
       <c r="C335" s="1"/>
-      <c r="D335" s="1"/>
+      <c r="D335" s="1">
+        <v>2500</v>
+      </c>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="3">
@@ -8849,7 +9128,9 @@
         <v>680</v>
       </c>
       <c r="C336" s="1"/>
-      <c r="D336" s="1"/>
+      <c r="D336" s="1">
+        <v>1500</v>
+      </c>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="3">
@@ -8867,7 +9148,9 @@
         <v>682</v>
       </c>
       <c r="C337" s="1"/>
-      <c r="D337" s="1"/>
+      <c r="D337" s="1">
+        <v>3000</v>
+      </c>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="3">
@@ -8885,7 +9168,9 @@
         <v>683</v>
       </c>
       <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
+      <c r="D338" s="1">
+        <v>3500</v>
+      </c>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="3">
@@ -8903,7 +9188,9 @@
         <v>684</v>
       </c>
       <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
+      <c r="D339" s="1">
+        <v>500</v>
+      </c>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="3">
@@ -8921,7 +9208,9 @@
         <v>686</v>
       </c>
       <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
+      <c r="D340" s="1">
+        <v>8000</v>
+      </c>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="3">
@@ -8939,7 +9228,9 @@
         <v>689</v>
       </c>
       <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
+      <c r="D341" s="1">
+        <v>15000</v>
+      </c>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="3">
@@ -8957,7 +9248,9 @@
         <v>691</v>
       </c>
       <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
+      <c r="D342" s="1">
+        <v>35000</v>
+      </c>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="3">
@@ -8975,7 +9268,9 @@
         <v>693</v>
       </c>
       <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
+      <c r="D343" s="1">
+        <v>55000</v>
+      </c>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="3">
@@ -8993,7 +9288,9 @@
         <v>695</v>
       </c>
       <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
+      <c r="D344" s="1">
+        <v>50000</v>
+      </c>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="3">
@@ -9011,7 +9308,9 @@
         <v>697</v>
       </c>
       <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
+      <c r="D345" s="1">
+        <v>85000</v>
+      </c>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="3">
@@ -9029,7 +9328,9 @@
         <v>699</v>
       </c>
       <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
+      <c r="D346" s="1">
+        <v>200000</v>
+      </c>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="3">
@@ -9047,7 +9348,9 @@
         <v>701</v>
       </c>
       <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
+      <c r="D347" s="1">
+        <v>320000</v>
+      </c>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="3">
